--- a/artfynd/A 28840-2025 artfynd.xlsx
+++ b/artfynd/A 28840-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482630</v>
       </c>
       <c r="B2" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28840-2025 artfynd.xlsx
+++ b/artfynd/A 28840-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482630</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28840-2025 artfynd.xlsx
+++ b/artfynd/A 28840-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482630</v>
       </c>
       <c r="B2" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28840-2025 artfynd.xlsx
+++ b/artfynd/A 28840-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482630</v>
       </c>
       <c r="B2" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28840-2025 artfynd.xlsx
+++ b/artfynd/A 28840-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482630</v>
       </c>
       <c r="B2" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28840-2025 artfynd.xlsx
+++ b/artfynd/A 28840-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482630</v>
       </c>
       <c r="B2" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28840-2025 artfynd.xlsx
+++ b/artfynd/A 28840-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482630</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28840-2025 artfynd.xlsx
+++ b/artfynd/A 28840-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482630</v>
       </c>
       <c r="B2" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28840-2025 artfynd.xlsx
+++ b/artfynd/A 28840-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482630</v>
       </c>
       <c r="B2" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28840-2025 artfynd.xlsx
+++ b/artfynd/A 28840-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136482630</v>
+        <v>137490372</v>
       </c>
       <c r="B2" t="n">
-        <v>93426</v>
+        <v>92456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>810552</v>
+        <v>810531</v>
       </c>
       <c r="R2" t="n">
-        <v>7255509</v>
+        <v>7255495</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,6 +775,210 @@
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137490372</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137490375</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92185</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Svartnäsmyran-Månsgrönnan, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>810531</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7255495</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137490375</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136482630</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93485</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svartnäsmyran-Månsgrönnan, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>810552</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7255509</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136482630</t>
         </is>
@@ -783,6 +987,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28840-2025 artfynd.xlsx
+++ b/artfynd/A 28840-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137490372</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137490375</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136482630</v>
       </c>
       <c r="B4" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
